--- a/data/wc2026_fixtures.xlsx
+++ b/data/wc2026_fixtures.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WC 2026 Fixtures" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WC 2026 Fixtures'!$A$1:$L$73</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,34 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-        <bgColor rgb="00D6E4F0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -76,22 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,24 +425,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>מספר משחק</t>
@@ -538,3895 +491,4582 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" t="n">
         <v>19609127</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>מקסיקו</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" t="n">
         <v>18576</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>דרום אפריקה</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" t="n">
         <v>18555</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" t="n">
         <v>19609153</v>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>02:00</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Korea Republic</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>קוריאה הדרומית</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" t="n">
         <v>18567</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>צ'כיה</t>
         </is>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" t="n">
         <v>18718</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" t="n">
         <v>19609154</v>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>קנדה</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" t="n">
         <v>18572</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Bosnia and Herzegovina</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>בוסניה והרצגובינה</t>
         </is>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" t="n">
         <v>18625</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" t="n">
         <v>19609133</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>01:00</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>ארצות הברית</t>
         </is>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" t="n">
         <v>18571</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>פרגוואי</t>
         </is>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" t="n">
         <v>18723</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" t="n">
         <v>19609155</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>01:00</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>האיטי</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" t="n">
         <v>18804</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Scotland</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>סקוטלנד</t>
         </is>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" t="n">
         <v>18706</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" t="n">
         <v>19609156</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>04:00</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>אוסטרליה</t>
         </is>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" t="n">
         <v>18730</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Türkiye</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>טורקיה</t>
         </is>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" t="n">
         <v>18716</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" t="n">
         <v>19609131</v>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>ברזיל</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" t="n">
         <v>18704</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>מרוקו</t>
         </is>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L8" t="n">
         <v>18551</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" t="n">
         <v>19609130</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>קטאר</t>
         </is>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" t="n">
         <v>18544</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>שוויץ</t>
         </is>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L9" t="n">
         <v>18708</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" t="n">
         <v>19609157</v>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>חוף השנהב</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" t="n">
         <v>18560</v>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>אקוודור</t>
         </is>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="L10" t="n">
         <v>18573</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" t="n">
         <v>19609158</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>גרמניה</t>
         </is>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" t="n">
         <v>18660</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Curacao</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>קוראסאו</t>
         </is>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="L11" t="n">
         <v>18910</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" t="n">
         <v>19609138</v>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>הולנד</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" t="n">
         <v>18694</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>יפן</t>
         </is>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="L12" t="n">
         <v>18597</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" t="n">
         <v>19609159</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>02:00</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>שוודיה</t>
         </is>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" t="n">
         <v>18564</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>תוניסיה</t>
         </is>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="L13" t="n">
         <v>18554</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" t="n">
         <v>19609161</v>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>ערב הסעודית</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" t="n">
         <v>18562</v>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>אורוגוואי</t>
         </is>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="L14" t="n">
         <v>15251</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" t="n">
         <v>19609162</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>ספרד</t>
         </is>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" t="n">
         <v>18710</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Cape Verde Islands</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>כף ורדה</t>
         </is>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="L15" t="n">
         <v>18823</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" t="n">
         <v>19609160</v>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>01:00</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>איראן</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" t="n">
         <v>18652</v>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>ניו זילנד</t>
         </is>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="L16" t="n">
         <v>18613</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" t="n">
         <v>19609139</v>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>בלגיה</t>
         </is>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" t="n">
         <v>18743</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>מצרים</t>
         </is>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="L17" t="n">
         <v>18546</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" t="n">
         <v>19609143</v>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>צרפת</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I18" t="n">
         <v>18647</v>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>סנגל</t>
         </is>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="L18" t="n">
         <v>18558</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" t="n">
         <v>19609163</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Iraq</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>עיראק</t>
         </is>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" t="n">
         <v>18600</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>נורווגיה</t>
         </is>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="L19" t="n">
         <v>18578</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" t="n">
         <v>19609145</v>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>01:00</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>ארגנטינה</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I20" t="n">
         <v>18644</v>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Algeria</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>אלג'יריה</t>
         </is>
       </c>
-      <c r="L20" s="2" t="n">
+      <c r="L20" t="n">
         <v>18620</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" t="n">
         <v>19609164</v>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>04:00</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>אוסטריה</t>
         </is>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I21" t="n">
         <v>18643</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>ירדן</t>
         </is>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L21" t="n">
         <v>18559</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" t="n">
         <v>19609167</v>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>גאנה</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="I22" t="n">
         <v>18553</v>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>פנמה</t>
         </is>
       </c>
-      <c r="L22" s="2" t="n">
+      <c r="L22" t="n">
         <v>18717</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" t="n">
         <v>19609149</v>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>אנגליה</t>
         </is>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I23" t="n">
         <v>18645</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>קרואטיה</t>
         </is>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" t="n">
         <v>18588</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" t="n">
         <v>19609166</v>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>פורטוגל</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I24" t="n">
         <v>18701</v>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Congo DR</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>קונגו</t>
         </is>
       </c>
-      <c r="L24" s="2" t="n">
+      <c r="L24" t="n">
         <v>18552</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" t="n">
         <v>19609165</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>02:00</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Uzbekistan</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>אוזבקיסטן</t>
         </is>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="I25" t="n">
         <v>18745</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>קולומביה</t>
         </is>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="L25" t="n">
         <v>18720</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" t="n">
         <v>19609168</v>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>צ'כיה</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="I26" t="n">
         <v>18718</v>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>דרום אפריקה</t>
         </is>
       </c>
-      <c r="L26" s="2" t="n">
+      <c r="L26" t="n">
         <v>18555</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" t="n">
         <v>19609169</v>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>שוויץ</t>
         </is>
       </c>
-      <c r="I27" s="4" t="n">
+      <c r="I27" t="n">
         <v>18708</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Bosnia and Herzegovina</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>בוסניה והרצגובינה</t>
         </is>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="L27" t="n">
         <v>18625</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" t="n">
         <v>19609170</v>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>קנדה</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="I28" t="n">
         <v>18572</v>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>קטאר</t>
         </is>
       </c>
-      <c r="L28" s="2" t="n">
+      <c r="L28" t="n">
         <v>18544</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" t="n">
         <v>19609128</v>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>01:00</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>מקסיקו</t>
         </is>
       </c>
-      <c r="I29" s="4" t="n">
+      <c r="I29" t="n">
         <v>18576</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Korea Republic</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>קוריאה הדרומית</t>
         </is>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="L29" t="n">
         <v>18567</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" t="n">
         <v>19609172</v>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>00:30</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>ברזיל</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="I30" t="n">
         <v>18704</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>האיטי</t>
         </is>
       </c>
-      <c r="L30" s="2" t="n">
+      <c r="L30" t="n">
         <v>18804</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" t="n">
         <v>19609171</v>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Scotland</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>סקוטלנד</t>
         </is>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="I31" t="n">
         <v>18706</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>מרוקו</t>
         </is>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="L31" t="n">
         <v>18551</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" t="n">
         <v>19609173</v>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>03:00</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Türkiye</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>טורקיה</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="I32" t="n">
         <v>18716</v>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>פרגוואי</t>
         </is>
       </c>
-      <c r="L32" s="2" t="n">
+      <c r="L32" t="n">
         <v>18723</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" t="n">
         <v>19609134</v>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>ארצות הברית</t>
         </is>
       </c>
-      <c r="I33" s="4" t="n">
+      <c r="I33" t="n">
         <v>18571</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>אוסטרליה</t>
         </is>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="L33" t="n">
         <v>18730</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" t="n">
         <v>19609135</v>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>גרמניה</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
+      <c r="I34" t="n">
         <v>18660</v>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>חוף השנהב</t>
         </is>
       </c>
-      <c r="L34" s="2" t="n">
+      <c r="L34" t="n">
         <v>18560</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="n">
+      <c r="B35" t="n">
         <v>19609174</v>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>אקוודור</t>
         </is>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="I35" t="n">
         <v>18573</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Curacao</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>קוראסאו</t>
         </is>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="L35" t="n">
         <v>18910</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" t="n">
         <v>19609176</v>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>הולנד</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="I36" t="n">
         <v>18694</v>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>שוודיה</t>
         </is>
       </c>
-      <c r="L36" s="2" t="n">
+      <c r="L36" t="n">
         <v>18564</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="B37" t="n">
         <v>19609175</v>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>04:00</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>תוניסיה</t>
         </is>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="I37" t="n">
         <v>18554</v>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>יפן</t>
         </is>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="L37" t="n">
         <v>18597</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" t="n">
         <v>19609178</v>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>אורוגוואי</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="I38" t="n">
         <v>15251</v>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Cape Verde Islands</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>כף ורדה</t>
         </is>
       </c>
-      <c r="L38" s="2" t="n">
+      <c r="L38" t="n">
         <v>18823</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="n">
+      <c r="B39" t="n">
         <v>19609142</v>
       </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>ספרד</t>
         </is>
       </c>
-      <c r="I39" s="4" t="n">
+      <c r="I39" t="n">
         <v>18710</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>ערב הסעודית</t>
         </is>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="L39" t="n">
         <v>18562</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B40" t="n">
         <v>19609152</v>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>בלגיה</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
+      <c r="I40" t="n">
         <v>18743</v>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>איראן</t>
         </is>
       </c>
-      <c r="L40" s="2" t="n">
+      <c r="L40" t="n">
         <v>18652</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="n">
+      <c r="B41" t="n">
         <v>19609177</v>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>01:00</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>ניו זילנד</t>
         </is>
       </c>
-      <c r="I41" s="4" t="n">
+      <c r="I41" t="n">
         <v>18613</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>מצרים</t>
         </is>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="L41" t="n">
         <v>18546</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B42" t="n">
         <v>19609180</v>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>נורווגיה</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="I42" t="n">
         <v>18578</v>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>סנגל</t>
         </is>
       </c>
-      <c r="L42" s="2" t="n">
+      <c r="L42" t="n">
         <v>18558</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="4" t="n">
+      <c r="B43" t="n">
         <v>19609179</v>
       </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>צרפת</t>
         </is>
       </c>
-      <c r="I43" s="4" t="n">
+      <c r="I43" t="n">
         <v>18647</v>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Iraq</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>עיראק</t>
         </is>
       </c>
-      <c r="L43" s="4" t="n">
+      <c r="L43" t="n">
         <v>18600</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="n">
+      <c r="B44" t="n">
         <v>19609146</v>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>ארגנטינה</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
+      <c r="I44" t="n">
         <v>18644</v>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>אוסטריה</t>
         </is>
       </c>
-      <c r="L44" s="2" t="n">
+      <c r="L44" t="n">
         <v>18643</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="4" t="n">
+      <c r="B45" t="n">
         <v>19609181</v>
       </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>03:00</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>ירדן</t>
         </is>
       </c>
-      <c r="I45" s="4" t="n">
+      <c r="I45" t="n">
         <v>18559</v>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Algeria</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>אלג'יריה</t>
         </is>
       </c>
-      <c r="L45" s="4" t="n">
+      <c r="L45" t="n">
         <v>18620</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="n">
+      <c r="B46" t="n">
         <v>19609183</v>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>אנגליה</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="I46" t="n">
         <v>18645</v>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>גאנה</t>
         </is>
       </c>
-      <c r="L46" s="2" t="n">
+      <c r="L46" t="n">
         <v>18553</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="4" t="n">
+      <c r="B47" t="n">
         <v>19609151</v>
       </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>פנמה</t>
         </is>
       </c>
-      <c r="I47" s="4" t="n">
+      <c r="I47" t="n">
         <v>18717</v>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>קרואטיה</t>
         </is>
       </c>
-      <c r="L47" s="4" t="n">
+      <c r="L47" t="n">
         <v>18588</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="n">
+      <c r="B48" t="n">
         <v>19609148</v>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>פורטוגל</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
+      <c r="I48" t="n">
         <v>18701</v>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Uzbekistan</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>אוזבקיסטן</t>
         </is>
       </c>
-      <c r="L48" s="2" t="n">
+      <c r="L48" t="n">
         <v>18745</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="4" t="n">
+      <c r="B49" t="n">
         <v>19609182</v>
       </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>02:00</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>קולומביה</t>
         </is>
       </c>
-      <c r="I49" s="4" t="n">
+      <c r="I49" t="n">
         <v>18720</v>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Congo DR</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>קונגו</t>
         </is>
       </c>
-      <c r="L49" s="4" t="n">
+      <c r="L49" t="n">
         <v>18552</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="n">
+      <c r="B50" t="n">
         <v>19609132</v>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Scotland</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>סקוטלנד</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="I50" t="n">
         <v>18706</v>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>ברזיל</t>
         </is>
       </c>
-      <c r="L50" s="2" t="n">
+      <c r="L50" t="n">
         <v>18704</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="4" t="n">
+      <c r="B51" t="n">
         <v>19609187</v>
       </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>מרוקו</t>
         </is>
       </c>
-      <c r="I51" s="4" t="n">
+      <c r="I51" t="n">
         <v>18551</v>
       </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
       </c>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>האיטי</t>
         </is>
       </c>
-      <c r="L51" s="4" t="n">
+      <c r="L51" t="n">
         <v>18804</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B52" t="n">
         <v>19609129</v>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>שוויץ</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="I52" t="n">
         <v>18708</v>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="K52" s="3" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>קנדה</t>
         </is>
       </c>
-      <c r="L52" s="2" t="n">
+      <c r="L52" t="n">
         <v>18572</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B53" t="n">
         <v>19609186</v>
       </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Bosnia and Herzegovina</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>בוסניה והרצגובינה</t>
         </is>
       </c>
-      <c r="I53" s="4" t="n">
+      <c r="I53" t="n">
         <v>18625</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>קטאר</t>
         </is>
       </c>
-      <c r="L53" s="4" t="n">
+      <c r="L53" t="n">
         <v>18544</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="n">
+      <c r="B54" t="n">
         <v>19609185</v>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>01:00</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>צ'כיה</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="I54" t="n">
         <v>18718</v>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>מקסיקו</t>
         </is>
       </c>
-      <c r="L54" s="2" t="n">
+      <c r="L54" t="n">
         <v>18576</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="4" t="n">
+      <c r="B55" t="n">
         <v>19609184</v>
       </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>01:00</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>דרום אפריקה</t>
         </is>
       </c>
-      <c r="I55" s="4" t="n">
+      <c r="I55" t="n">
         <v>18555</v>
       </c>
-      <c r="J55" s="4" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>Korea Republic</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>קוריאה הדרומית</t>
         </is>
       </c>
-      <c r="L55" s="4" t="n">
+      <c r="L55" t="n">
         <v>18567</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" t="n">
         <v>19609191</v>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Curacao</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>קוראסאו</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
+      <c r="I56" t="n">
         <v>18910</v>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="K56" s="3" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>חוף השנהב</t>
         </is>
       </c>
-      <c r="L56" s="2" t="n">
+      <c r="L56" t="n">
         <v>18560</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
+      <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="4" t="n">
+      <c r="B57" t="n">
         <v>19609136</v>
       </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>אקוודור</t>
         </is>
       </c>
-      <c r="I57" s="4" t="n">
+      <c r="I57" t="n">
         <v>18573</v>
       </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>גרמניה</t>
         </is>
       </c>
-      <c r="L57" s="4" t="n">
+      <c r="L57" t="n">
         <v>18660</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="n">
+      <c r="B58" t="n">
         <v>19609190</v>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>יפן</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
+      <c r="I58" t="n">
         <v>18597</v>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="K58" s="3" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>שוודיה</t>
         </is>
       </c>
-      <c r="L58" s="2" t="n">
+      <c r="L58" t="n">
         <v>18564</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="4" t="n">
+      <c r="B59" t="n">
         <v>19609137</v>
       </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>תוניסיה</t>
         </is>
       </c>
-      <c r="I59" s="4" t="n">
+      <c r="I59" t="n">
         <v>18554</v>
       </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>הולנד</t>
         </is>
       </c>
-      <c r="L59" s="4" t="n">
+      <c r="L59" t="n">
         <v>18694</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B60" t="n">
         <v>19609189</v>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>02:00</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Türkiye</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>טורקיה</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
+      <c r="I60" t="n">
         <v>18716</v>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="K60" s="3" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>ארצות הברית</t>
         </is>
       </c>
-      <c r="L60" s="2" t="n">
+      <c r="L60" t="n">
         <v>18571</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="4" t="n">
+      <c r="B61" t="n">
         <v>19609188</v>
       </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>02:00</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>פרגוואי</t>
         </is>
       </c>
-      <c r="I61" s="4" t="n">
+      <c r="I61" t="n">
         <v>18723</v>
       </c>
-      <c r="J61" s="4" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>אוסטרליה</t>
         </is>
       </c>
-      <c r="L61" s="4" t="n">
+      <c r="L61" t="n">
         <v>18730</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="2" t="n">
+      <c r="B62" t="n">
         <v>19609144</v>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>נורווגיה</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="I62" t="n">
         <v>18578</v>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="K62" s="3" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>צרפת</t>
         </is>
       </c>
-      <c r="L62" s="2" t="n">
+      <c r="L62" t="n">
         <v>18647</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
+      <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="4" t="n">
+      <c r="B63" t="n">
         <v>19609195</v>
       </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>סנגל</t>
         </is>
       </c>
-      <c r="I63" s="4" t="n">
+      <c r="I63" t="n">
         <v>18558</v>
       </c>
-      <c r="J63" s="4" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>Iraq</t>
         </is>
       </c>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>עיראק</t>
         </is>
       </c>
-      <c r="L63" s="4" t="n">
+      <c r="L63" t="n">
         <v>18600</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="n">
+      <c r="B64" t="n">
         <v>19609193</v>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>03:00</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>מצרים</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="I64" t="n">
         <v>18546</v>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="K64" s="3" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>איראן</t>
         </is>
       </c>
-      <c r="L64" s="2" t="n">
+      <c r="L64" t="n">
         <v>18652</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
+      <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="4" t="n">
+      <c r="B65" t="n">
         <v>19609192</v>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>03:00</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>ניו זילנד</t>
         </is>
       </c>
-      <c r="I65" s="4" t="n">
+      <c r="I65" t="n">
         <v>18613</v>
       </c>
-      <c r="J65" s="4" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="K65" s="5" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>בלגיה</t>
         </is>
       </c>
-      <c r="L65" s="4" t="n">
+      <c r="L65" t="n">
         <v>18743</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B66" t="n">
         <v>19609194</v>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Cape Verde Islands</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>כף ורדה</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
+      <c r="I66" t="n">
         <v>18823</v>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="K66" s="3" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>ערב הסעודית</t>
         </is>
       </c>
-      <c r="L66" s="2" t="n">
+      <c r="L66" t="n">
         <v>18562</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
+      <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="4" t="n">
+      <c r="B67" t="n">
         <v>19609141</v>
       </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>אורוגוואי</t>
         </is>
       </c>
-      <c r="I67" s="4" t="n">
+      <c r="I67" t="n">
         <v>15251</v>
       </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>ספרד</t>
         </is>
       </c>
-      <c r="L67" s="4" t="n">
+      <c r="L67" t="n">
         <v>18710</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="2" t="n">
+      <c r="B68" t="n">
         <v>19609199</v>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>פנמה</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
+      <c r="I68" t="n">
         <v>18717</v>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K68" s="3" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>אנגליה</t>
         </is>
       </c>
-      <c r="L68" s="2" t="n">
+      <c r="L68" t="n">
         <v>18645</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
+      <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="4" t="n">
+      <c r="B69" t="n">
         <v>19609150</v>
       </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>קרואטיה</t>
         </is>
       </c>
-      <c r="I69" s="4" t="n">
+      <c r="I69" t="n">
         <v>18588</v>
       </c>
-      <c r="J69" s="4" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="K69" s="5" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>גאנה</t>
         </is>
       </c>
-      <c r="L69" s="4" t="n">
+      <c r="L69" t="n">
         <v>18553</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="2" t="n">
+      <c r="B70" t="n">
         <v>19609197</v>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>02:00</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Algeria</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>אלג'יריה</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
+      <c r="I70" t="n">
         <v>18620</v>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="K70" s="3" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>אוסטריה</t>
         </is>
       </c>
-      <c r="L70" s="2" t="n">
+      <c r="L70" t="n">
         <v>18643</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n">
+      <c r="A71" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="4" t="n">
+      <c r="B71" t="n">
         <v>19609198</v>
       </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>3</v>
+      </c>
+      <c r="E71" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>02:00</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>ירדן</t>
         </is>
       </c>
-      <c r="I71" s="4" t="n">
+      <c r="I71" t="n">
         <v>18559</v>
       </c>
-      <c r="J71" s="4" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>ארגנטינה</t>
         </is>
       </c>
-      <c r="L71" s="4" t="n">
+      <c r="L71" t="n">
         <v>18644</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="2" t="n">
+      <c r="B72" t="n">
         <v>19609147</v>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>קולומביה</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
+      <c r="I72" t="n">
         <v>18720</v>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="K72" s="3" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>פורטוגל</t>
         </is>
       </c>
-      <c r="L72" s="2" t="n">
+      <c r="L72" t="n">
         <v>18701</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n">
+      <c r="A73" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="4" t="n">
+      <c r="B73" t="n">
         <v>19609196</v>
       </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>Group Stage</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Group Stage</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Congo DR</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>קונגו</t>
         </is>
       </c>
-      <c r="I73" s="4" t="n">
+      <c r="I73" t="n">
         <v>18552</v>
       </c>
-      <c r="J73" s="4" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>Uzbekistan</t>
         </is>
       </c>
-      <c r="K73" s="5" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>אוזבקיסטן</t>
         </is>
       </c>
-      <c r="L73" s="4" t="n">
+      <c r="L73" t="n">
         <v>18745</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>19700073</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ברזיל</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>יפן</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>19700074</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>דרום אפריקה</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>קנדה</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="n">
+        <v>19700075</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>גרמניה</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>פרגוואי</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>19700076</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>הולנד</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>מרוקו</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>19700077</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>חוף השנהב</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>נורווגיה</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="n">
+        <v>19700078</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>צרפת</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>שוודיה</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="n">
+        <v>19700079</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>מקסיקו</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>אקוודור</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="n">
+        <v>19700080</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>אנגליה</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Congo DR</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>קונגו DR</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="n">
+        <v>19700081</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>בלגיה</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>סנגל</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="n">
+        <v>19700082</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ארה"ב</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Bosnia &amp; Herzegovina</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>בוסניה והרצגובינה</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="n">
+        <v>19700083</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ספרד</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>אוסטריה</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="n">
+        <v>19700084</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>פורטוגל</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>קרואטיה</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="n">
+        <v>19700085</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>שוויץ</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>אלג'יריה</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="n">
+        <v>19700086</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>אוסטרליה</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>מצרים</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="n">
+        <v>19700087</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ארגנטינה</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Cape Verde Islands</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>כף ורדה</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="n">
+        <v>19700088</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>קולומביה</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>גאנה</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>